--- a/for_test/test_db4.xlsx
+++ b/for_test/test_db4.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
+  </numFmts>
   <fonts count="1">
     <font>
       <name val="Calibri"/>
@@ -46,8 +49,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -464,66 +469,58 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Updated normal text</t>
+          <t>Just normal text with letters and numbers 123</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Updated problematic chars with new line \n and tab \t.</t>
+          <t>This has "quotes", a backslash \\, a newline \n, and a tab \t.</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>99</v>
+        <v>42</v>
       </c>
       <c r="E2" t="n">
-        <v>5.55</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>2025-10-28</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>2025-10-28 16:00:00</t>
-        </is>
+        <v>3.14</v>
+      </c>
+      <c r="F2" s="1" t="n">
+        <v>45957</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>45957.64583333334</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>New record normal string</t>
+          <t>Another normal string</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>New problematic chars.</t>
+          <t>More problematic chars: ''single quotes'', /slashes/, and control characters like \0 or \r\n.</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>200</v>
+        <v>-100</v>
       </c>
       <c r="E3" t="n">
-        <v>12.34</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>2021-01-01</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>2021-01-01 01:00:00</t>
-        </is>
+        <v>99.98999999999999</v>
+      </c>
+      <c r="F3" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>43831</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
